--- a/03_code/Auswertung_Datenpunkte_staff_workshop.xlsx
+++ b/03_code/Auswertung_Datenpunkte_staff_workshop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikla\Desktop\Universität_Regensburg\KI-Workshop\Paper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikla\Documents\GitHub\GenerativeAI Guidelines in Informatics Education\03_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84239C05-90B4-404D-85A5-864FB45F2136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC183EC4-B415-4CE0-9638-E81C1E16FC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-18120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Punkteverteilung" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
     <t>Learning Support</t>
   </si>
   <si>
-    <t>Brainstroming</t>
-  </si>
-  <si>
     <t>Task</t>
   </si>
   <si>
@@ -78,7 +75,10 @@
     <t>Studienplanung</t>
   </si>
   <si>
-    <t>Study Preperation</t>
+    <t>Brainstorming</t>
+  </si>
+  <si>
+    <t>Study Preparation</t>
   </si>
 </sst>
 </file>
@@ -405,10 +405,10 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1">
         <v>1</v>
@@ -476,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>1.5</v>
@@ -612,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -677,10 +677,10 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -748,7 +748,7 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -816,7 +816,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -881,10 +881,10 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>7</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>0</v>
